--- a/6. boardrepo/BoardRepo_Requirements_v0_22.xlsx
+++ b/6. boardrepo/BoardRepo_Requirements_v0_22.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rebd13f6fddd540e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requirements" sheetId="2" r:id="R3502e8c779f44ece"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conflict Analysis" sheetId="3" r:id="Ra543c5c5186b4b5a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability" sheetId="4" r:id="R7ca75b304fb44ccc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Cases" sheetId="5" r:id="R186b72ce83fa4843"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="6" r:id="R27c37d75649b4e14"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="References" sheetId="7" r:id="Rb654047b57c74793"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R620ef10befae4d9e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requirements" sheetId="2" r:id="Ra1669a3e24534b82"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conflict Analysis" sheetId="3" r:id="R953fad4a606e45b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Traceability" sheetId="4" r:id="R94dc0e8cd8e44218"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Cases" sheetId="5" r:id="R9b531105dd2549c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="6" r:id="R98399e0e322c4d59"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="References" sheetId="7" r:id="R34682d168d464b1e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -208,7 +208,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RequirementsTable" displayName="RequirementsTable" ref="A1:K265" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="RequirementsTable" displayName="RequirementsTable" ref="A1:K267" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="11">
     <x:tableColumn id="1" name="Req ID"/>
     <x:tableColumn id="2" name="Category"/>
@@ -227,7 +227,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ConflictTable" displayName="ConflictTable" ref="A1:F193" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ConflictTable" displayName="ConflictTable" ref="A1:F195" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="6">
     <x:tableColumn id="1" name="Req A"/>
     <x:tableColumn id="2" name="Req B"/>
@@ -241,7 +241,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="TraceabilityTable" displayName="TraceabilityTable" ref="A1:E265" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="TraceabilityTable" displayName="TraceabilityTable" ref="A1:E267" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="5">
     <x:tableColumn id="1" name="Req ID"/>
     <x:tableColumn id="2" name="Design/Module"/>
@@ -254,7 +254,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="TestCasesTable" displayName="TestCasesTable" ref="A1:H265" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="TestCasesTable" displayName="TestCasesTable" ref="A1:H267" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="TC ID"/>
     <x:tableColumn id="2" name="Req ID"/>
@@ -270,7 +270,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="ChangeLogTable" displayName="ChangeLogTable" ref="A1:D29" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="ChangeLogTable" displayName="ChangeLogTable" ref="A1:D30" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="Version"/>
     <x:tableColumn id="2" name="Date"/>
@@ -517,7 +517,7 @@
         <x:v>Total Requirements</x:v>
       </x:c>
       <x:c r="B4" s="19" t="n">
-        <x:v>264</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="C4" s="19"/>
       <x:c r="D4" s="19"/>
@@ -529,8 +529,8 @@
         <x:v>Implemented</x:v>
       </x:c>
       <x:c r="B5" s="19" t="n">
-        <x:f>COUNTIF(Requirements!$F$2:$F$265,"Implemented")</x:f>
-        <x:v>226</x:v>
+        <x:f>COUNTIF(Requirements!$F$2:$F$267,"Implemented")</x:f>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="C5" s="19"/>
       <x:c r="D5" s="19"/>
@@ -542,7 +542,7 @@
         <x:v>Planned</x:v>
       </x:c>
       <x:c r="B6" s="19" t="n">
-        <x:f>COUNTIF(Requirements!$F$2:$F$265,"Planned")</x:f>
+        <x:f>COUNTIF(Requirements!$F$2:$F$267,"Planned")</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="C6" s="19"/>
@@ -568,7 +568,7 @@
         <x:v>Test Cases</x:v>
       </x:c>
       <x:c r="B8" s="19" t="n">
-        <x:v>264</x:v>
+        <x:v>266</x:v>
       </x:c>
       <x:c r="C8" s="19"/>
       <x:c r="D8" s="19"/>
@@ -580,8 +580,8 @@
         <x:v>Superseded</x:v>
       </x:c>
       <x:c r="B9" s="19" t="n">
-        <x:f>COUNTIF(Requirements!$F$2:$F$265,"Superseded")</x:f>
-        <x:v>36</x:v>
+        <x:f>COUNTIF(Requirements!$F$2:$F$267,"Superseded")</x:f>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C9" s="19"/>
       <x:c r="D9" s="19"/>
@@ -670,16 +670,16 @@
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="19" t="str">
-        <x:v>Git Recovery Boundary</x:v>
+        <x:v>Git Alias Boundary</x:v>
       </x:c>
       <x:c r="B15" s="19" t="str">
-        <x:v>BoardRepo = transport</x:v>
+        <x:v>Git Manager only</x:v>
       </x:c>
       <x:c r="C15" s="19" t="str">
-        <x:v>Git Manager = recovery</x:v>
+        <x:v>BoardRepo v0.22 unchanged</x:v>
       </x:c>
       <x:c r="D15" s="19" t="str">
-        <x:v>No auto Git action</x:v>
+        <x:v>No engine intrusion</x:v>
       </x:c>
       <x:c r="E15" s="19"/>
       <x:c r="F15" s="19"/>
@@ -689,7 +689,7 @@
         <x:v>Package Release</x:v>
       </x:c>
       <x:c r="B16" t="str">
-        <x:v>260819_1</x:v>
+        <x:v>260819_2</x:v>
       </x:c>
       <x:c r="C16" t="str">
         <x:v>Technical Version</x:v>
@@ -9807,7 +9807,7 @@
         <x:v>Must</x:v>
       </x:c>
       <x:c r="F265" s="19" t="str">
-        <x:v>Implemented</x:v>
+        <x:v>Superseded</x:v>
       </x:c>
       <x:c r="G265" s="19" t="str">
         <x:v>TC-264</x:v>
@@ -9818,9 +9818,79 @@
       <x:c r="I265" s="19" t="str">
         <x:v>260819_1 / v0.22 Metadata</x:v>
       </x:c>
-      <x:c r="J265" s="19" t="str"/>
+      <x:c r="J265" s="19" t="str">
+        <x:v>260819_1 package 기준선은 이력으로 유지. 현재 integration-aligned package는 BR-266의 260819_2. Technical v0.22 유지.</x:v>
+      </x:c>
       <x:c r="K265" s="19" t="str">
         <x:f>IF(COUNTIFS('Conflict Analysis'!$A:$A,A265,'Conflict Analysis'!$F:$F,"OPEN")+COUNTIFS('Conflict Analysis'!$B:$B,A265,'Conflict Analysis'!$F:$F,"OPEN")&gt;0,"OPEN CONFLICT","OK")</x:f>
+        <x:v>OK</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="266">
+      <x:c r="A266" s="19" t="str">
+        <x:v>BR-265</x:v>
+      </x:c>
+      <x:c r="B266" s="19" t="str">
+        <x:v>Integration</x:v>
+      </x:c>
+      <x:c r="C266" s="19" t="str">
+        <x:v>Git Manager의 legacy Git Tree alias 상태판정 수정과 recovery URL 자동화는 target 5 책임이며 BoardRepo v0.22의 게시판 업로드/다운로드/브라우저/중복검사 기능을 변경하지 않아야 한다.</x:v>
+      </x:c>
+      <x:c r="D266" s="19" t="str">
+        <x:v>Git Manager patch가 BoardRepo 엔진으로 침범하는 것을 방지</x:v>
+      </x:c>
+      <x:c r="E266" s="19" t="str">
+        <x:v>Must</x:v>
+      </x:c>
+      <x:c r="F266" s="19" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="G266" s="19" t="str">
+        <x:v>TC-265</x:v>
+      </x:c>
+      <x:c r="H266" s="19" t="str">
+        <x:v>Git Manager boundary / BoardRepo v0.22</x:v>
+      </x:c>
+      <x:c r="I266" s="19" t="str">
+        <x:v>Git Alias Patch Boundary</x:v>
+      </x:c>
+      <x:c r="J266" s="19" t="str"/>
+      <x:c r="K266" s="19" t="str">
+        <x:f>IF(COUNTIFS('Conflict Analysis'!$A:$A,A266,'Conflict Analysis'!$F:$F,"OPEN")+COUNTIFS('Conflict Analysis'!$B:$B,A266,'Conflict Analysis'!$F:$F,"OPEN")&gt;0,"OPEN CONFLICT","OK")</x:f>
+        <x:v>OK</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="267">
+      <x:c r="A267" s="19" t="str">
+        <x:v>BR-266</x:v>
+      </x:c>
+      <x:c r="B267" s="19" t="str">
+        <x:v>Packaging</x:v>
+      </x:c>
+      <x:c r="C267" s="19" t="str">
+        <x:v>현재 BoardRepo package release는 BoardRepo_260819_2.zip이며 Technical Version은 v0.22를 유지하고 최신 BoardRepo 요구사항을 동봉해야 한다.</x:v>
+      </x:c>
+      <x:c r="D267" s="19" t="str">
+        <x:v>Automation Manager/Git Manager 260819_2 기준선과 package release 정렬</x:v>
+      </x:c>
+      <x:c r="E267" s="19" t="str">
+        <x:v>Must</x:v>
+      </x:c>
+      <x:c r="F267" s="19" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="G267" s="19" t="str">
+        <x:v>TC-266</x:v>
+      </x:c>
+      <x:c r="H267" s="19" t="str">
+        <x:v>config.json, package metadata</x:v>
+      </x:c>
+      <x:c r="I267" s="19" t="str">
+        <x:v>260819_2 / v0.22 Metadata</x:v>
+      </x:c>
+      <x:c r="J267" s="19" t="str"/>
+      <x:c r="K267" s="19" t="str">
+        <x:f>IF(COUNTIFS('Conflict Analysis'!$A:$A,A267,'Conflict Analysis'!$F:$F,"OPEN")+COUNTIFS('Conflict Analysis'!$B:$B,A267,'Conflict Analysis'!$F:$F,"OPEN")&gt;0,"OPEN CONFLICT","OK")</x:f>
         <x:v>OK</x:v>
       </x:c>
     </x:row>
@@ -9833,7 +9903,7 @@
       <x:formula>K2="OK"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:dataValidations count="62">
+  <x:dataValidations count="64">
     <x:dataValidation type="list" sqref="E2:E35">
       <x:formula1>"Must,Should,Could"</x:formula1>
     </x:dataValidation>
@@ -10020,10 +10090,16 @@
     <x:dataValidation type="list" sqref="F2:F265">
       <x:formula1>"Implemented,Planned,Deferred,Superseded"</x:formula1>
     </x:dataValidation>
+    <x:dataValidation type="list" sqref="E266:E267">
+      <x:formula1>"Must,Should,Could"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="F2:F267">
+      <x:formula1>"Implemented,Planned,Deferred,Superseded"</x:formula1>
+    </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb636586ddbcf4644"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R251d2f8143ef4a42"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13900,6 +13976,46 @@
         <x:v>Resolved</x:v>
       </x:c>
     </x:row>
+    <x:row r="194">
+      <x:c r="A194" t="str">
+        <x:v>BR-265</x:v>
+      </x:c>
+      <x:c r="B194" t="str">
+        <x:v>BR-262</x:v>
+      </x:c>
+      <x:c r="C194" t="str">
+        <x:v>Git recovery responsibility boundary와 신규 Git alias patch</x:v>
+      </x:c>
+      <x:c r="D194" t="str">
+        <x:v>Git 상태 fix 때문에 BoardRepo 엔진을 수정할 위험</x:v>
+      </x:c>
+      <x:c r="E194" t="str">
+        <x:v>Git Tree alias/recovery URL 수정은 target 5 Git Manager에만 적용, BoardRepo 기능코드는 유지</x:v>
+      </x:c>
+      <x:c r="F194" t="str">
+        <x:v>Resolved</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="195">
+      <x:c r="A195" t="str">
+        <x:v>BR-266</x:v>
+      </x:c>
+      <x:c r="B195" t="str">
+        <x:v>BR-264</x:v>
+      </x:c>
+      <x:c r="C195" t="str">
+        <x:v>BoardRepo 260819_1/v0.22와 통합 260819_2</x:v>
+      </x:c>
+      <x:c r="D195" t="str">
+        <x:v>기능 변경 없이 package release 정렬</x:v>
+      </x:c>
+      <x:c r="E195" t="str">
+        <x:v>Technical v0.22 유지, Package Release만 260819_2</x:v>
+      </x:c>
+      <x:c r="F195" t="str">
+        <x:v>Resolved</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="F2:F8">
     <x:cfRule type="expression" dxfId="4" priority="1">
@@ -13916,7 +14032,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b10b82e382e4425"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06b7dddc02204085"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18363,16 +18479,50 @@
         <x:v>TC-264</x:v>
       </x:c>
       <x:c r="D265" t="str">
-        <x:v>Implemented</x:v>
+        <x:v>Superseded</x:v>
       </x:c>
       <x:c r="E265" t="str">
         <x:v>v0.22 / 260819_1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="266">
+      <x:c r="A266" t="str">
+        <x:v>BR-265</x:v>
+      </x:c>
+      <x:c r="B266" t="str">
+        <x:v>Git Manager boundary / BoardRepo unchanged</x:v>
+      </x:c>
+      <x:c r="C266" t="str">
+        <x:v>TC-265</x:v>
+      </x:c>
+      <x:c r="D266" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="E266" t="str">
+        <x:v>v0.22 / 260819_2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="267">
+      <x:c r="A267" t="str">
+        <x:v>BR-266</x:v>
+      </x:c>
+      <x:c r="B267" t="str">
+        <x:v>config.json / package metadata</x:v>
+      </x:c>
+      <x:c r="C267" t="str">
+        <x:v>TC-266</x:v>
+      </x:c>
+      <x:c r="D267" t="str">
+        <x:v>Implemented</x:v>
+      </x:c>
+      <x:c r="E267" t="str">
+        <x:v>v0.22 / 260819_2</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R371bb40864fb4027"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb13f6a8b3ae4926"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -24813,9 +24963,59 @@
         <x:v>BoardRepo_260819_1 / v0.22 / 최신 Excel 일치</x:v>
       </x:c>
       <x:c r="G265" s="19" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
+      <x:c r="H265" s="19" t="str">
+        <x:v>현재 package 검증은 TC-266으로 이관.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="266">
+      <x:c r="A266" s="19" t="str">
+        <x:v>TC-265</x:v>
+      </x:c>
+      <x:c r="B266" s="19" t="str">
+        <x:v>BR-265</x:v>
+      </x:c>
+      <x:c r="C266" s="19" t="str">
+        <x:v>Regression</x:v>
+      </x:c>
+      <x:c r="D266" s="19" t="str">
+        <x:v>260819_1/2 BoardRepo function hashes</x:v>
+      </x:c>
+      <x:c r="E266" s="19" t="str">
+        <x:v>기능코드 비교</x:v>
+      </x:c>
+      <x:c r="F266" s="19" t="str">
+        <x:v>BoardRepo function/GUI 파일 byte-identical</x:v>
+      </x:c>
+      <x:c r="G266" s="19" t="str">
         <x:v>Not Run</x:v>
       </x:c>
-      <x:c r="H265" s="19" t="str"/>
+      <x:c r="H266" s="19" t="str"/>
+    </x:row>
+    <x:row r="267">
+      <x:c r="A267" s="19" t="str">
+        <x:v>TC-266</x:v>
+      </x:c>
+      <x:c r="B267" s="19" t="str">
+        <x:v>BR-266</x:v>
+      </x:c>
+      <x:c r="C267" s="19" t="str">
+        <x:v>Packaging</x:v>
+      </x:c>
+      <x:c r="D267" s="19" t="str">
+        <x:v>최종 BoardRepo ZIP/config/requirements</x:v>
+      </x:c>
+      <x:c r="E267" s="19" t="str">
+        <x:v>배포 검사</x:v>
+      </x:c>
+      <x:c r="F267" s="19" t="str">
+        <x:v>BoardRepo_260819_2 / v0.22 / 최신 Excel 일치</x:v>
+      </x:c>
+      <x:c r="G267" s="19" t="str">
+        <x:v>Not Run</x:v>
+      </x:c>
+      <x:c r="H267" s="19" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="G2:G35">
@@ -24826,7 +25026,7 @@
       <x:formula>G2="Fail"</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:dataValidations count="29">
+  <x:dataValidations count="30">
     <x:dataValidation type="list" sqref="G2:G35">
       <x:formula1>"Not Run,Pass,Fail,N/A"</x:formula1>
     </x:dataValidation>
@@ -24914,10 +25114,13 @@
     <x:dataValidation type="list" sqref="G263:G265">
       <x:formula1>"Not Run,Pass,Fail,N/A"</x:formula1>
     </x:dataValidation>
+    <x:dataValidation type="list" sqref="G266:G267">
+      <x:formula1>"Not Run,Pass,Fail,N/A"</x:formula1>
+    </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9c3855b467a94fb0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8c15ec2deea444d1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25338,10 +25541,24 @@
         <x:v>Automation Manager/Git Manager self-bootstrap Git recovery 추가에 맞춰 BoardRepo Package Release를 260819_1로 정렬. BoardRepo 기능 Technical Version v0.22 유지. BoardRepo는 target 5/6 Release 운반/staging만 담당하며 Git 연결/Push를 호출하지 않는 책임 경계 명시.</x:v>
       </x:c>
     </x:row>
+    <x:row r="30">
+      <x:c r="A30" t="str">
+        <x:v>0.22 / 260819_2</x:v>
+      </x:c>
+      <x:c r="B30" t="str">
+        <x:v>2026-08-19</x:v>
+      </x:c>
+      <x:c r="C30" t="str">
+        <x:v>Integration Package Alignment</x:v>
+      </x:c>
+      <x:c r="D30" t="str">
+        <x:v>Git Manager legacy Git Tree alias/복구 URL UX 수정에 맞춰 BoardRepo Package Release만 260819_2로 정렬. BoardRepo Technical v0.22와 기능 코드는 변경하지 않음.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc4d42b11d7f047d3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re07500e1dbda4a80"/>
   </x:tableParts>
 </x:worksheet>
 </file>
